--- a/data/trans_camb/P16A08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,13</t>
+          <t>-1,63; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,18</t>
+          <t>-1,98; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,86</t>
+          <t>-2,1; 5,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,7</t>
+          <t>-0,02; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,48</t>
+          <t>-1,02; 4,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,41</t>
+          <t>-3,06; 3,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,42</t>
+          <t>-0,26; 3,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,16</t>
+          <t>-0,45; 3,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,14</t>
+          <t>-1,86; 3,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 148,11</t>
+          <t>-38,53; 131,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 130,55</t>
+          <t>-43,15; 123,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,86; 206,79</t>
+          <t>-56,93; 212,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 200,49</t>
+          <t>-4,28; 212,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 163,95</t>
+          <t>-23,06; 168,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 129,15</t>
+          <t>-67,61; 133,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 119,7</t>
+          <t>-6,6; 120,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 112,35</t>
+          <t>-11,88; 112,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 110,72</t>
+          <t>-46,59; 101,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,48</t>
+          <t>-0,54; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,92</t>
+          <t>-0,88; 3,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,92</t>
+          <t>0,22; 6,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,71</t>
+          <t>-0,55; 4,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,55</t>
+          <t>-0,92; 4,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 46,66</t>
+          <t>1,53; 48,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,28</t>
+          <t>0,15; 3,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,25</t>
+          <t>-0,05; 3,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 31,09</t>
+          <t>2,36; 31,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 205,47</t>
+          <t>-21,51; 212,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 179,69</t>
+          <t>-27,29; 180,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 397,26</t>
+          <t>0,42; 379,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 150,38</t>
+          <t>-13,08; 166,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 142,77</t>
+          <t>-18,9; 137,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,51; 1365,81</t>
+          <t>32,57; 1451,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 126,96</t>
+          <t>1,73; 120,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 124,28</t>
+          <t>-3,09; 119,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,15; 1090,18</t>
+          <t>67,4; 1113,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,0</t>
+          <t>0,27; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,07</t>
+          <t>-0,44; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,07</t>
+          <t>-0,03; 4,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,87</t>
+          <t>0,82; 5,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,42</t>
+          <t>0,43; 5,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,97</t>
+          <t>-1,24; 3,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,29</t>
+          <t>1,15; 4,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,45</t>
+          <t>0,54; 3,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,76</t>
+          <t>-0,13; 2,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 350,07</t>
+          <t>6,78; 337,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 291,75</t>
+          <t>-21,16; 287,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 357,26</t>
+          <t>-4,41; 361,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,5; 182,69</t>
+          <t>14,79; 196,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 186,22</t>
+          <t>5,0; 180,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 100,75</t>
+          <t>-23,96; 106,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,78; 171,28</t>
+          <t>30,6; 170,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 144,93</t>
+          <t>13,86; 145,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 117,9</t>
+          <t>-3,57; 117,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,0</t>
+          <t>-1,91; 2,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,62</t>
+          <t>-2,19; 1,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,71</t>
+          <t>-1,54; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,09</t>
+          <t>0,12; 5,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,74</t>
+          <t>-0,4; 4,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,79</t>
+          <t>0,35; 4,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,81</t>
+          <t>-0,33; 2,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,5</t>
+          <t>-0,49; 2,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,57</t>
+          <t>-0,68; 3,52</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 168,98</t>
+          <t>-62,47; 228,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 167,06</t>
+          <t>-65,24; 185,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 307,35</t>
+          <t>-43,16; 323,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 241,36</t>
+          <t>-4,0; 237,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 223,59</t>
+          <t>-10,72; 198,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 221,45</t>
+          <t>3,91; 236,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 144,41</t>
+          <t>-9,95; 159,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 124,17</t>
+          <t>-18,95; 131,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 185,11</t>
+          <t>-13,8; 183,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,58</t>
+          <t>-2,98; 1,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,9</t>
+          <t>-1,29; 3,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,63</t>
+          <t>-3,08; 0,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,04</t>
+          <t>-4,99; 0,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,23</t>
+          <t>-2,74; 3,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,82</t>
+          <t>-3,49; 1,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,33</t>
+          <t>-3,11; 0,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,7</t>
+          <t>-1,29; 2,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,68</t>
+          <t>-2,73; 0,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 148,79</t>
+          <t>-72,24; 135,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 275,7</t>
+          <t>-33,2; 276,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,68; 49,7</t>
+          <t>-75,45; 77,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-69,12; 42,59</t>
+          <t>-71,69; 23,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 90,65</t>
+          <t>-41,62; 91,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 55,8</t>
+          <t>-48,6; 51,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 15,8</t>
+          <t>-61,61; 19,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 93,8</t>
+          <t>-26,55; 107,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 24,91</t>
+          <t>-52,64; 20,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,72</t>
+          <t>-0,18; 5,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,66</t>
+          <t>-2,69; 1,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,74</t>
+          <t>-2,04; 1,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,81</t>
+          <t>-3,29; 2,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,29</t>
+          <t>-4,39; 1,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,46</t>
+          <t>-5,26; 0,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,0</t>
+          <t>-1,13; 2,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,93</t>
+          <t>-2,81; 0,67</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,72</t>
+          <t>-3,05; 0,63</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 751,28</t>
+          <t>-34,25; 810,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 267,78</t>
+          <t>-89,14; 233,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 248,65</t>
+          <t>-67,83; 249,48</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 98,78</t>
+          <t>-54,98; 93,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-71,48; 44,96</t>
+          <t>-67,51; 55,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,7; 13,29</t>
+          <t>-79,76; 13,32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 122,04</t>
+          <t>-27,92; 118,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 41,53</t>
+          <t>-64,31; 33,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 27,43</t>
+          <t>-70,9; 23,15</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 5,14</t>
+          <t>-1,74; 5,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,43</t>
+          <t>-2,21; 3,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,2</t>
+          <t>-3,12; 1,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,65</t>
+          <t>-1,4; 3,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,2</t>
+          <t>-1,34; 4,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,48</t>
+          <t>-2,31; 2,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,52</t>
+          <t>-0,76; 3,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,49</t>
+          <t>-0,8; 3,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,63</t>
+          <t>-1,86; 1,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,97; 537,78</t>
+          <t>-56,19; 555,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,93; 405,34</t>
+          <t>-61,8; 291,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-72,65; 257,79</t>
+          <t>-73,19; 209,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 331,5</t>
+          <t>-43,57; 345,3</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 304,79</t>
+          <t>-44,17; 383,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 271,55</t>
+          <t>-55,59; 212,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 265,79</t>
+          <t>-26,46; 269,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 283,67</t>
+          <t>-26,25; 250,4</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 118,8</t>
+          <t>-50,12; 121,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,88</t>
+          <t>0,18; 1,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,4</t>
+          <t>-0,06; 1,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,86</t>
+          <t>-0,12; 1,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,67</t>
+          <t>0,65; 2,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,56</t>
+          <t>0,4; 2,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,91</t>
+          <t>0,23; 9,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,98</t>
+          <t>0,63; 2,02</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,74</t>
+          <t>0,46; 1,82</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,37</t>
+          <t>0,47; 4,89</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,65; 96,05</t>
+          <t>5,3; 91,58</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 68,55</t>
+          <t>-2,85; 80,58</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 91,51</t>
+          <t>-4,78; 91,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,64; 80,68</t>
+          <t>14,54; 73,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,81; 75,47</t>
+          <t>9,13; 71,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,96; 253,6</t>
+          <t>4,68; 235,28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,21; 69,95</t>
+          <t>18,32; 72,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>11,56; 59,29</t>
+          <t>12,58; 62,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12,63; 164,9</t>
+          <t>14,3; 158,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,18</t>
+          <t>-1,7; 3,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,12</t>
+          <t>-1,47; 3,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,11</t>
+          <t>-2,68; 3,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,52</t>
+          <t>-0,39; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,86</t>
+          <t>-0,71; 4,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,33</t>
+          <t>-2,81; 3,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,46</t>
+          <t>-0,38; 3,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,31</t>
+          <t>-0,65; 3,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,27</t>
+          <t>-2,04; 2,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>-1,09%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-14,06%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 131,45</t>
+          <t>-39,17; 150,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 123,71</t>
+          <t>-36,49; 145,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,93; 212,34</t>
+          <t>-64,07; 140,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 212,72</t>
+          <t>-10,69; 191,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 168,66</t>
+          <t>-17,83; 187,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,61; 133,79</t>
+          <t>-64,82; 137,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 120,14</t>
+          <t>-8,86; 120,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 112,28</t>
+          <t>-17,43; 110,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 101,11</t>
+          <t>-49,3; 87,75</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,16</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>2,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,58</t>
+          <t>-0,51; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,07</t>
+          <t>-0,84; 3,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,77</t>
+          <t>0,21; 5,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,81</t>
+          <t>-0,51; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,31</t>
+          <t>-0,54; 4,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 48,33</t>
+          <t>-0,17; 5,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,21</t>
+          <t>0,18; 3,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,16</t>
+          <t>-0,21; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 31,47</t>
+          <t>0,74; 4,91</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124,07%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>360,14%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>298,87%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 212,5</t>
+          <t>-17,3; 204,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 180,94</t>
+          <t>-26,4; 199,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 379,67</t>
+          <t>1,73; 338,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 166,03</t>
+          <t>-10,24; 150,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 137,6</t>
+          <t>-11,79; 157,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,57; 1451,19</t>
+          <t>-5,27; 183,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 120,77</t>
+          <t>0,9; 131,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 119,08</t>
+          <t>-7,34; 115,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,4; 1113,13</t>
+          <t>17,06; 185,62</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,11</t>
+          <t>0,38; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,39</t>
+          <t>-0,59; 3,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,18</t>
+          <t>0,16; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,97</t>
+          <t>0,73; 5,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,44</t>
+          <t>0,47; 5,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,03</t>
+          <t>-1,38; 2,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,11</t>
+          <t>1,19; 4,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,58</t>
+          <t>0,46; 3,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,82</t>
+          <t>-0,34; 2,74</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101,1%</t>
+          <t>100,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 337,18</t>
+          <t>-1,81; 348,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 287,69</t>
+          <t>-25,86; 256,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 361,48</t>
+          <t>1,78; 341,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,79; 196,13</t>
+          <t>12,29; 180,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,0; 180,26</t>
+          <t>6,23; 161,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 106,04</t>
+          <t>-27,43; 96,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,6; 170,47</t>
+          <t>27,8; 187,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,86; 145,38</t>
+          <t>11,76; 159,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 117,36</t>
+          <t>-8,27; 115,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>3,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,14</t>
+          <t>-1,86; 2,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,64</t>
+          <t>-2,02; 1,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,85</t>
+          <t>0,38; 4,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,03</t>
+          <t>0,04; 4,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,31</t>
+          <t>-0,29; 4,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,76</t>
+          <t>1,19; 5,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,94</t>
+          <t>-0,28; 3,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,52</t>
+          <t>-0,57; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,52</t>
+          <t>1,57; 4,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>129,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>107,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>117,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,47; 228,74</t>
+          <t>-62,51; 197,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 185,94</t>
+          <t>-70,3; 157,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 323,04</t>
+          <t>-1,69; 459,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 237,12</t>
+          <t>-3,28; 229,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 198,42</t>
+          <t>-13,43; 224,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 236,19</t>
+          <t>23,71; 267,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 159,92</t>
+          <t>-10,34; 159,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 131,27</t>
+          <t>-16,52; 123,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 183,22</t>
+          <t>40,22; 256,24</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,53</t>
+          <t>-2,94; 1,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,9</t>
+          <t>-1,13; 3,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,81</t>
+          <t>-3,17; 1,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,68</t>
+          <t>-4,51; 0,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,25</t>
+          <t>-2,65; 3,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,66</t>
+          <t>-3,59; 1,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,43</t>
+          <t>-3,13; 0,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,9</t>
+          <t>-1,2; 2,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,6</t>
+          <t>-2,46; 0,65</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-36,78%</t>
+          <t>-32,15%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,12%</t>
+          <t>-13,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-22,2%</t>
+          <t>-20,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,24; 135,15</t>
+          <t>-77,58; 108,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 276,26</t>
+          <t>-34,05; 270,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 77,91</t>
+          <t>-74,77; 83,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,69; 23,2</t>
+          <t>-68,38; 24,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 91,33</t>
+          <t>-42,34; 104,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 51,6</t>
+          <t>-50,63; 44,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 19,0</t>
+          <t>-62,54; 17,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 107,7</t>
+          <t>-24,57; 103,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 20,36</t>
+          <t>-48,01; 25,44</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,22</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,55</t>
+          <t>-0,27; 5,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,43</t>
+          <t>-2,38; 1,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,8</t>
+          <t>-2,17; 1,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,76</t>
+          <t>-3,31; 2,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,4</t>
+          <t>-4,24; 1,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,64</t>
+          <t>-3,05; 1,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,85</t>
+          <t>-1,03; 3,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,67</t>
+          <t>-2,65; 0,74</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,63</t>
+          <t>-1,97; 1,2</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-41,42%</t>
+          <t>-8,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-27,91%</t>
+          <t>-6,69%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 810,11</t>
+          <t>-36,7; 652,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,14; 233,67</t>
+          <t>-84,0; 305,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 249,48</t>
+          <t>-72,22; 238,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 93,75</t>
+          <t>-56,94; 74,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 55,11</t>
+          <t>-69,44; 55,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,76; 13,32</t>
+          <t>-50,17; 62,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 118,46</t>
+          <t>-26,05; 133,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 33,25</t>
+          <t>-62,32; 32,82</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 23,15</t>
+          <t>-43,45; 56,35</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,05</t>
+          <t>-1,67; 5,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,35</t>
+          <t>-2,33; 3,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,9</t>
+          <t>-2,77; 2,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,85</t>
+          <t>-1,42; 3,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,36</t>
+          <t>-1,21; 4,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,25</t>
+          <t>-2,08; 2,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,56</t>
+          <t>-0,78; 3,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,38</t>
+          <t>-0,75; 3,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,64</t>
+          <t>-1,46; 1,85</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-4,05%</t>
+          <t>-3,74%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-56,19; 555,42</t>
+          <t>-63,99; 538,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,8; 291,03</t>
+          <t>-64,6; 334,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-73,19; 209,55</t>
+          <t>-66,8; 240,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 345,3</t>
+          <t>-41,93; 378,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 383,84</t>
+          <t>-45,97; 430,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 212,92</t>
+          <t>-51,16; 255,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 269,69</t>
+          <t>-28,1; 273,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 250,4</t>
+          <t>-26,03; 260,07</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-50,12; 121,96</t>
+          <t>-41,46; 141,01</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,85</t>
+          <t>0,18; 1,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,57</t>
+          <t>-0,06; 1,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,88</t>
+          <t>0,21; 1,9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,6</t>
+          <t>0,59; 2,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,44</t>
+          <t>0,42; 2,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,71</t>
+          <t>0,2; 1,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,02</t>
+          <t>0,63; 1,99</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,82</t>
+          <t>0,47; 1,74</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,89</t>
+          <t>0,44; 1,67</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5,3; 91,58</t>
+          <t>6,84; 94,11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 80,58</t>
+          <t>-3,24; 73,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 91,82</t>
+          <t>6,55; 97,89</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,54; 73,49</t>
+          <t>12,61; 75,44</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,13; 71,14</t>
+          <t>9,21; 70,27</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,68; 235,28</t>
+          <t>4,44; 60,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,32; 72,09</t>
+          <t>18,32; 69,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>12,58; 62,45</t>
+          <t>13,65; 61,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14,3; 158,08</t>
+          <t>12,79; 58,1</t>
         </is>
       </c>
     </row>
